--- a/data_extactor/batch_10_fa/batch_0049_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0049_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار پرونده الکترونیک سلامت Electronic medical record EMR | نرم‌افزار دوربین گاما Gamma camera software | نرم‌افزار MEDITECH | نرم‌افزار Medovation RadRunner | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | پایگاه‌های داده موجودی داروسازی هسته‌ای</t>
+          <t>نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار دوربین گاما Gamma camera software | نرم‌افزار MEDITECH | نرم‌افزار Medovation RadRunner | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | پایگاه‌های داده موجودی رادیودارو</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب خواندن | مانیتورینگ | نگارش | علوم پایه | ریاضیات | یادگیری فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | نگارش | علوم | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | زیست‌شناسی | زبان انگلیسی | فیزیک | پزشکی و دندانپزشکی | شیمی | کامپیوتر و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | امور اداری | آموزش و تربیت | روانشناسی</t>
+          <t>خدمات مشتری و شخصی | زیست‌شناسی | زبان انگلیسی | فیزیک | پزشکی و دندان‌پزشکی | شیمی | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | اداری | آموزش و پرورش | روان‌شناسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مشکلات | درک کتبی | سازماندهی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | استدلال قیاسی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | سهولت کار با اعداد | استدلال ریاضی | دقت کنترل | ثبات دست و بازو | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | درک کتبی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | استدلال قیاسی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | استدلال ریاضی | دقت کنترل | ثبات دست و بازو | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض تشعشع | ارتباط با دیگران | مکالمات تلفنی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | اهمیت دقیق یا منظم بودن | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | پیامد اشتباه | کار با یا مشارکت در یک گروه کاری یا تیم | داخل ساختمان، محیط کنترل‌شده | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | ایمیل | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظ تشعشع | سلامت و ایمنی سایر کارکنان</t>
+          <t>قرار گرفتن در معرض تابش | ارتباط با دیگران | مکالمات تلفنی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | اهمیت دقیق یا درست بودن | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | نزدیکی فیزیکی | پیامد خطا | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فشار زمانی | ایمیل | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان قلب و عروق | تکنولوژیست‌ها و تکنسین‌های قلب و عروق | تکنولوژیست‌های سیتوژنتیک | سونوگرافیست‌های تشخیص پزشکی | پزشکان طب اورژانس | تکنسین‌های بافت‌شناسی | هیستوتکنولوژیست‌ها | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | دوزیمتریست‌های پزشکی | آماده‌سازان تجهیزات پزشکی | تکنسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنسین‌های پایش هسته‌ای | تکنولوژیست‌های پزشکی چشم‌پزشکی | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | تکنولوژیست‌های جراحی</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | تکنولوژیست‌های سیتوژنتیک | سونوگرافیست‌های پزشکی تشخیصی | پزشکان طب اورژانس | تکنیسین‌های هیستولوژی | هیستوتکنولوژیست‌ها | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | دوزیمتریست‌های پزشکی | آماده‌سازان تجهیزات پزشکی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنسین‌های نظارت هسته‌ای | تکنولوژیست‌های پزشکی چشم‌پزشکی | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار کدگذاری تشخیصی و فرآیندی | نرم‌افزار بررسی تصویر تشخیصی | نرم‌افزار ارتباطات تصویر دیجیتال در پزشکی DICOM/نرم‌افزار مدیریت مدالیته | نرم‌افزار پرونده الکترونیک سلامت Electronic medical record EMR | نرم‌افزار ردیابی و مدیریت پردازشگر فیلم | GE Healthcare Centricity EMR | GE Healthcare ViewPoint Solutions | نرم‌افزار زیرسیستم مدیریت اطلاعات | نرم‌افزار یکپارچه‌سازی سیستم‌های اطلاعاتی | نرم‌افزار توزیع تصویر اینترنت یا اینترانت | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری فرآیندهای پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار مدیریت مطب PMS | R | نرم‌افزار ورود داده‌های ساختاریافته | نرم‌افزار تصویربرداری توموگرافی کامپیوتری CT واقعیت مجازی | نرم‌افزار eClinicalWorks EHR</t>
+          <t>نرم‌افزار کدگذاری تشخیصی و فرآیندی | نرم‌افزار بررسی تصویر تشخیصی | نرم‌افزار ارتباطات تصویر دیجیتال در پزشکی DICOM/نرم‌افزار مدیریت مدالیته | نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار ردیابی و مدیریت پردازشگر فیلم | GE Healthcare Centricity EMR | GE Healthcare ViewPoint Solutions | نرم‌افزار زیرسیستم مدیریت اطلاعات | نرم‌افزار یکپارچه‌سازی سیستم‌های اطلاعاتی | نرم‌افزار توزیع تصویر اینترنت یا اینترانت | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی | نرم‌افزار کدگذاری رویه‌های پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار مدیریت مطب PMS | R | نرم‌افزار ورود داده‌های ساختاریافته | نرم‌افزار تصویربرداری توموگرافی کامپیوتری CT واقعیت مجازی | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب خواندن | سخن گفتن | مانیتورینگ | تفکر انتقادی | نگارش</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نظارت | تفکر انتقادی | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و پرسنلی | زبان انگلیسی | کامپیوتر و الکترونیک | امور اداری | آموزش و تربیت | ایمنی و امنیت عمومی | روانشناسی | فیزیک | زیست‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | اداری | آموزش و پرورش | ایمنی و امنیت عمومی | روان‌شناسی | فیزیک | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مشکلات | بینایی نزدیک | بیان شفاهی | درک کتبی | استدلال قیاسی | سازماندهی اطلاعات | وضوح گفتار | تشخیص گفتار | استدلال استقرایی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | دقت کنترل | ثبات دست و بازو | توجه انتخابی | تجسم فضایی | بیان کتبی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | بیان شفاهی | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | استدلال استقرایی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | دقت کنترل | ثبات دست و بازو | توجه انتخابی | تجسم | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | مکالمات تلفنی | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | اهمیت دقیق یا منظم بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | داخل ساختمان، محیط کنترل‌شده | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ایمیل | قرار گرفتن در معرض تشعشع | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظ تشعشع | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | فشار زمانی | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن</t>
+          <t>ارتباط با دیگران | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | مکالمات تلفنی | فراوانی تصمیم‌گیری | نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | ایمیل | قرار گرفتن در معرض تابش | تأثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای انجام حرکات تکراری | فشار زمانی | صرف زمان برای راه رفتن یا دویدن | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان قلب و عروق | تکنولوژیست‌ها و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیص پزشکی | تکنسین‌های آندوسکوپی | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | دستیاران پزشک | تکنسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | جراحان ارتوپد، به جز اطفال | جراحان اطفال | پرتودرمانگران | رادیولوژیست‌ها | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | سونوگرافیست‌های پزشکی تشخیصی | تکنسین‌های آندوسکوپی | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | دستیاران پزشکی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پرتودرمانگران | رادیولوژیست‌ها | درمانگران تنفسی | دستیاران جراحی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,32 +617,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>نرم‌افزار برنامه‌ریزی نوبت | نرم‌افزار پرونده الکترونیک سلامت Electronic medical record EMR | GE Healthcare Centricity EMR | نرم‌افزار MEDITECH | نرم‌افزار پردازش تصویر پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | سیستم‌های اطلاعات رادیولوژی (RIS) | سیستم‌های تله‌رادیولوژی | نرم‌افزار مرورگر وب | نرم‌افزار eClinicalWorks EHR</t>
+          <t>نرم‌افزار زمان‌بندی قرار ملاقات | نرم‌افزار پرونده الکترونیک سلامت EMR | GE Healthcare Centricity EMR | نرم‌افزار MEDITECH | نرم‌افزار پردازش تصویر پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | سیستم‌های اطلاعات رادیولوژی (RIS) | سیستم‌های تله‌رادیولوژی | نرم‌افزار مرورگر وب | نرم‌افزار eClinicalWorks EHR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب خواندن | گوش دادن فعال | مانیتورینگ | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | زبان انگلیسی | فیزیک | کامپیوتر و الکترونیک | ایمنی و امنیت عمومی | پزشکی و دندانپزشکی | آموزش و تربیت | زیست‌شناسی | روانشناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فیزیک | رایانه و الکترونیک | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | آموزش و پرورش | زیست‌شناسی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | درک کتبی | حساسیت به مشکلات | بیان کتبی | استدلال قیاسی | دقت کنترل | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | سازماندهی اطلاعات | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | زبردستی انگشتان | زبردستی دست | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | بینایی دور</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | درک کتبی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | دقت کنترل | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | بینایی دور</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا منظم بودن | داخل ساختمان، محیط کنترل‌شده | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | ایمیل | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تعیین وظایف، اولویت‌ها و اهداف | پیامد اشتباه | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش, کلاه ایمنی یا جلیقه نجات | فشار زمانی | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | سرعت تعیین‌شده توسط سرعت تجهیزات | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | آزادی در تصمیم‌گیری | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | تعیین وظایف، اولویت‌ها و اهداف | پیامد خطا | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | اهمیت تکرار وظایف یکسان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | نزدیکی فیزیکی | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | سرعت تعیین‌شده توسط سرعت تجهیزات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان قلب و عروق | تکنولوژیست‌ها و تکنسین‌های قلب و عروق | تکنولوژیست‌های سیتوژنتیک | سونوگرافیست‌های تشخیص پزشکی | تکنسین‌های آندوسکوپی | دوزیمتریست‌های پزشکی | تکنسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | جراحان ارتوپد، به جز اطفال | جراحان اطفال | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | درمانگران تنفسی | تکنولوژیست‌های جراحی</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | تکنولوژیست‌های سیتوژنتیک | سونوگرافیست‌های پزشکی تشخیصی | تکنسین‌های آندوسکوپی | دوزیمتریست‌های پزشکی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | درمانگران تنفسی | تکنولوژیست‌های جراحی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب خواندن | سخن گفتن | نگارش | ریاضیات | مانیتورینگ | علوم پایه | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | ریاضیات | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ریاضیات | فیزیک | کامپیوتر و الکترونیک | زیست‌شناسی | پزشکی و دندانپزشکی | زبان انگلیسی | طراحی | آموزش و تربیت | خدمات مشتریان و پرسنلی</t>
+          <t>ریاضیات | فیزیک | رایانه و الکترونیک | زیست‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | طراحی | آموزش و پرورش | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مشکلات | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | سازماندهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | سهولت کار با اعداد | انعطاف‌پذیری بستار | روان بودن ایده‌ها | بینایی دور | توجه انتخابی | تجسم فضایی | سرعت ادراکی | ابتکار</t>
+          <t>استدلال قیاسی | استدلال استقرایی | درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | توانایی عددی | انعطاف‌پذیری بستار | روانی ایده‌ها | بینایی دور | توجه انتخابی | تجسم | سرعت ادراکی | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>فشار زمانی | اهمیت دقیق یا منظم بودن | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | داخل ساختمان، محیط کنترل‌شده | پیامد اشتباه | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری</t>
+          <t>فشار زمانی | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | پیامد خطا | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | ارتباط با دیگران | صرف زمان برای انجام حرکات تکراری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | مهندسان زیستی و مهندسان پزشکی | متخصصان قلب و عروق | تکنولوژیست‌ها و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیص پزشکی | تکنسین‌های فوریت‌های پزشکی | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | تکنسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | تکنسین‌های پایش هسته‌ای | پرستاران بیهوشی | جراحان ارتوپد، به جز اطفال | پارامدیک‌ها | جراحان اطفال | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | درمانگران تنفسی</t>
+          <t>دستیاران متخصص بیهوشی | مهندسان زیستی و مهندسان زیست‌پزشکی | متخصصان قلب | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | سونوگرافیست‌های پزشکی تشخیصی | تکنسین‌های فوریت‌های پزشکی | تکنولوژیست‌های تصویربرداری تشدید مغناطیسی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | تکنولوژیست‌های پزشکی هسته‌ای | تکنسین‌های نظارت هسته‌ای | پرستاران بیهوشی | جراحان ارتوپد، به‌جز کودکان | پارامدیک‌ها | جراحان کودکان | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | رادیولوژیست‌ها | درمانگران تنفسی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب خواندن | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | مانیتورینگ | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و پرسنلی | ایمنی و امنیت عمومی | زبان انگلیسی | روانشناسی | زیست‌شناسی | حمل و نقل | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | روان‌شناسی | زیست‌شناسی | حمل و نقل | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مشکلات | سازماندهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | زبردستی انگشتان | ثبات دست و بازو | زبردستی دست | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم فضایی | اشتراک زمانی | زمان عکس‌العمل | قدرت استاتیک | قدرت تنه | استقامت | توجه شنیداری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | زمان عکس‌العمل | قدرت ایستا | قدرت تنه | استقامت | توجه شنیداری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | پیامد اشتباه | اهمیت دقیق یا منظم بودن | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | داخل ساختمان، محیط کنترل‌شده | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | خارج از ساختمان، قرار گرفتن در معرض تمام شرایط آب و هوایی | برخورد با افراد خشن یا از نظر فیزیکی تهاجمی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای خم شدن یا پیچش بدن | قرار گرفتن در معرض شرایط خطرناک</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، در معرض تمام شرایط آب و هوایی | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض شرایط خطرناک</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | رانندگان و همراهان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | تکنولوژیست‌ها و تکنسین‌های قلب و عروق | پرستاران مراقبت‌های ویژه | پزشکان طب اورژانس | کمک‌پرستاران خانگی | پرستاران عملی و حرفه‌ای دارای مجوز | دستیاران پزشک | پرستاران بیهوشی | پرستاران متخصص | کمک‌پرستاران | پارامدیک‌ها | دستیاران فیزیوتراپی | دستیاران پزشک | تکنسین‌های روانپزشکی | پرستاران ثبت‌شده | درمانگران تنفسی | دستیاران جراحی</t>
+          <t>پرستاران مراقبت‌های ویژه | رانندگان و متصدیان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | پرستاران بخش مراقبت‌های ویژه | پزشکان طب اورژانس | کمک‌یاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | پرستاران بیهوشی | پرستاران متخصص | کمک‌پرستاران | پارامدیک‌ها | کمک‌یاران فیزیوتراپی | دستیاران پزشک | تکنسین‌های روانپزشکی | پرستاران ثبت‌شده | درمانگران تنفسی | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب خواندن | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم پایه | مانیتورینگ | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندانپزشکی | خدمات مشتریان و پرسنلی | ایمنی و امنیت عمومی | زبان انگلیسی | روانشناسی | زیست‌شناسی | شیمی | حمل و نقل | درمان و مشاوره</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | روان‌شناسی | زیست‌شناسی | شیمی | حمل و نقل | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مشکلات | سازماندهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | زبردستی انگشتان | ثبات دست و بازو | زبردستی دست | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم فضایی | اشتراک زمانی | زمان عکس‌العمل | قدرت استاتیک | قدرت تنه | استقامت | توجه شنیداری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | زمان عکس‌العمل | قدرت ایستا | قدرت تنه | استقامت | توجه شنیداری</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | پیامد اشتباه | اهمیت دقیق یا منظم بودن | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | داخل ساختمان، محیط کنترل‌شده | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | خارج از ساختمان، قرار گرفتن در معرض تمام شرایط آب و هوایی | برخورد با افراد خشن یا از نظر فیزیکی تهاجمی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای خم شدن یا پیچش بدن | قرار گرفتن در معرض شرایط خطرناک</t>
+          <t>قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | نزدیکی فیزیکی | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | پیامد خطا | اهمیت دقیق یا درست بودن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | صرف زمان برای ایستادن | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، در معرض تمام شرایط آب و هوایی | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض شرایط خطرناک</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | رانندگان و همراهان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | تکنولوژیست‌ها و تکنسین‌های قلب و عروق | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان طب خانواده | پرستاران عملی و حرفه‌ای دارای مجوز | دستیاران پزشک | پرستاران بیهوشی | پرستاران ماما | پرستاران متخصص | کمک‌پرستاران | دستیاران پزشک | پرستاران ثبت‌شده | درمانگران تنفسی | دستیاران جراحی</t>
+          <t>پرستاران مراقبت‌های ویژه | رانندگان و متصدیان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | متخصصان پرستاری بالینی | پرستاران بخش مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان خانواده | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | پرستاران بیهوشی | ماماها | پرستاران متخصص | کمک‌پرستاران | دستیاران پزشک | پرستاران ثبت‌شده | درمانگران تنفسی | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار برنامه‌ریزی نوبت | Axxya Systems Nutritionist Pro | CBORD Nutrition Service Suite | Computrition Nutrition Care Management NCM Select | CyberSoft NutriBase | Cybersoft Primero Software Suite | DietMaster Systems Clinical Nutrition | ESHA Research The Food Processor | Food Service Solutions FoodCo | Gnutrition | LunchByte Systems NUTRIKIDS | نرم‌افزار MEDITECH | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | NutriGenie Optimal Nutrition | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | The Nutrition Company FoodWorks | پایگاه داده تغذیه کودکان USDA | ValuSoft MasterCook | نرم‌افزار مرورگر وب | eTritionWare</t>
+          <t>نرم‌افزار زمان‌بندی قرار ملاقات | Axxya Systems Nutritionist Pro | CBORD Nutrition Service Suite | Computrition Nutrition Care Management NCM Select | CyberSoft NutriBase | Cybersoft Primero Software Suite | DietMaster Systems Clinical Nutrition | ESHA Research The Food Processor | Food Service Solutions FoodCo | Gnutrition | LunchByte Systems NUTRIKIDS | نرم‌افزار MEDITECH | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | NutriGenie Optimal Nutrition | نرم‌افزار پرونده الکترونیک سلامت بیمار EMR | The Nutrition Company FoodWorks | پایگاه داده تغذیه کودکان USDA | ValuSoft MasterCook | نرم‌افزار مرورگر وب | eTritionWare</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری | مانیتورینگ | درک مطلب خواندن</t>
+          <t>سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | زبان انگلیسی | آموزش و تربیت | ریاضیات | ایمنی و امنیت عمومی | مدیریت و سازماندهی | تولید غذا | امور اداری | کامپیوتر و الکترونیک | تولید و فرآوری | پرسنل و منابع انسانی | قانون و حکومت</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | ریاضیات | ایمنی و امنیت عمومی | مدیریت و اداره | تولید مواد غذایی | اداری | رایانه و الکترونیک | تولید و فرآوری | پرسنل و منابع انسانی | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | وضوح گفتار | درک کتبی | حساسیت به مشکلات | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | سازماندهی اطلاعات | روان بودن ایده‌ها | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری بستار | ابتکار</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | وضوح گفتار | درک کتبی | حساسیت به مسئله | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری بستار | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ارتباط با دیگران | داخل ساختمان، محیط کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا منظم بودن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | نزدیکی فیزیکی | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | صرف زمان برای ایستادن | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | مکالمات تلفنی | موقعیت‌های تعارض | صرف زمان برای راه رفتن یا دویدن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | پیامدهای کاری و نتایج سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | صرف زمان برای ایستادن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فراوانی تصمیم‌گیری | مکالمات تلفنی | موقعیت‌های تعارض | صرف زمان برای راه رفتن یا دویدن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمونولوژی | پرستاران متخصص بالینی | کارکنان بهداشت جامعه | آشپزها، موسسات و سلف‌سرویس‌ها | متخصصان تغذیه و رژیم‌درمانی | فیزیولوژیست‌های ورزشی | معلمان علوم خانواده و مصرف‌کننده، مقطع پس از متوسطه | هماهنگ‌کنندگان تناسب اندام و تندرستی | دانشمندان و تکنولوژیست‌های مواد غذایی | مدیران خدمات غذایی | متخصصان آموزش بهداشت | کمک‌پرستاران خانگی | پرستاران عملی و حرفه‌ای دارای مجوز | دستیاران پزشک | مدیران خدمات پزشکی و بهداشتی | کمک‌پرستاران | پزشکان طب پیشگیری | تکنسین‌های روانپزشکی | پرستاران ثبت‌شده | مشاوران توانبخشی</t>
+          <t>متخصصان آلرژی و ایمونولوژی | متخصصان پرستاری بالینی | مددکاران سلامت جامعه | آشپزهای موسسات و سلف‌سرویس‌ها | متخصصان رژیم غذایی و تغذیه | فیزیولوژیست‌های ورزشی | اساتید علوم خانواده و مصرف‌کننده، پس از متوسطه | هماهنگ‌کنندگان تناسب اندام و سلامتی | دانشمندان و تکنولوژیست‌های علوم غذایی | مدیران خدمات غذایی | متخصصان آموزش بهداشت | کمک‌یاران سلامت در منزل | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | مدیران خدمات پزشکی و بهداشتی | کمک‌پرستاران | پزشکان طب پیشگیری | تکنسین‌های روانپزشکی | پرستاران ثبت‌شده | مشاوران توانبخشی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب خواندن | سخن گفتن | تفکر انتقادی | یادگیری فعال | مانیتورینگ | نگارش | ریاضیات</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | پزشکی و دندانپزشکی | ریاضیات | زبان انگلیسی | کامپیوتر و الکترونیک | قانون و حکومت | امور اداری | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | قانون و دولت | اداری | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | سازماندهی اطلاعات | حساسیت به مشکلات | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | بیان کتبی | زبردستی انگشتان | سرعت ادراکی | سهولت کار با اعداد | استدلال قیاسی | ثبات دست و بازو | اشتراک زمانی | توجه انتخابی | استدلال استقرایی | زبردستی دست</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | بیان کتبی | مهارت انگشتان | سرعت ادراکی | توانایی عددی | استدلال قیاسی | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | استدلال استقرایی | مهارت دستی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | اهمیت دقیق یا منظم بودن | داخل ساختمان، محیط کنترل‌شده | ارتباط با دیگران | ایمیل | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف یکسان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فشار زمانی | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | پیامد اشتباه | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | موقعیت‌های تعارض | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>مکالمات تلفنی | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای ایستادن | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت تکرار وظایف یکسان | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فشار زمانی | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | صرف زمان برای راه رفتن یا دویدن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | موقعیت‌های تعارض | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | تکنولوژیست‌ها و تکنسین‌های قلب و عروق | دستیاران دندانپزشکی | پرستاران عملی و حرفه‌ای دارای مجوز | دستیاران پزشک | آماده‌سازان تجهیزات پزشکی | متخصصان سوابق پزشکی | منشی‌های پزشکی و دستیاران اداری | تکنسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | مدیران خدمات پزشکی و بهداشتی | کمک‌پرستاران | تکنسین‌های پزشکی چشم‌پزشکی | عینک‌سازان، توزیع‌کننده | داروسازان | کمک‌داروسازان | فلبوتومیست‌ها | دستیاران جراحی | تکنولوژیست‌های جراحی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
+          <t>دستیاران متخصص بیهوشی | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | دستیاران دندان‌پزشکی | پرستاران عملی دارای مجوز و پرستاران حرفه‌ای دارای مجوز | دستیاران پزشکی | آماده‌سازان تجهیزات پزشکی | متخصصان مدارک پزشکی | منشی‌های پزشکی و دستیاران اداری | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | مدیران خدمات پزشکی و بهداشتی | کمک‌پرستاران | تکنسین‌های پزشکی چشم‌پزشکی | عینک‌سازان، توزیع‌کننده | داروسازان | دستیاران داروخانه | فلبوتومیست‌ها | دستیاران جراحی | تکنولوژیست‌های جراحی | تکنولوژیست‌ها و تکنسین‌های دامپزشکی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | سخن گفتن | درک مطلب خواندن | تفکر انتقادی | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>روانشناسی | درمان و مشاوره | زبان انگلیسی | خدمات مشتریان و پرسنلی | پزشکی و دندانپزشکی | آموزش و تربیت | ایمنی و امنیت عمومی | قانون و حکومت | کامپیوتر و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
+          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | آموزش و پرورش | ایمنی و امنیت عمومی | قانون و دولت | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مشکلات | استدلال قیاسی | استدلال استقرایی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | بینایی نزدیک | سازماندهی اطلاعات | توجه انتخابی | بینایی دور | انعطاف‌پذیری دسته‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | بینایی نزدیک | ترتیب‌دهی اطلاعات | توجه انتخابی | بینایی دور | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره به چهره با افراد و درون تیم‌ها | ارتباط با دیگران | مکالمات تلفنی | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | ایمیل | داخل ساختمان، محیط کنترل‌شده | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها، سطوح نویز که حواس‌پرت‌کننده یا ناراحت‌کننده هستند | اهمیت دقیق یا منظم بودن | سلامت و ایمنی سایر کارکنان | برخورد با افراد خشن یا از نظر فیزیکی تهاجمی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | مکالمات تلفنی | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | کار با یا مشارکت در یک گروه کاری یا تیم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | نامه‌ها و یادداشت‌های کتبی | آزادی در تصمیم‌گیری | صرف زمان برای ایستادن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | اهمیت دقیق یا درست بودن | سلامت و ایمنی سایر کارکنان | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت‌های ویژه | پرستاران روانپزشکی پیشرفته | پرستاران متخصص بالینی | روانشناسان بالینی و مشاوره | کمک‌پرستاران خانگی | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | پرستاران متخصص | کاردرمانگران | کمک‌کاردرمانگران | دستیاران کاردرمانی | پارامدیک‌ها | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌پرستاران روانپزشکی | روانپزشکان | تفریح‌درمانگران | پرستاران ثبت‌شده</t>
+          <t>پرستاران مراقبت‌های ویژه | پرستاران پیشرفته روانپزشکی | متخصصان پرستاری بالینی | روان‌شناسان بالینی و مشاوره | کمک‌یاران سلامت در منزل | مشاوران سلامت روان | مددکاران اجتماعی سلامت روان و سوء مصرف مواد | پرستاران متخصص | کاردرمانگران | کمک‌یاران کاردرمانی | دستیاران کاردرمانی | پارامدیک‌ها | پزشکان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | دستیاران فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران روان‌پزشکی | روان‌پزشکان | درمانگران تفریحی | پرستاران ثبت‌شده</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت Electronic medical record EMR | نرم‌افزار ایمیل | Google Drive | نرم‌افزار گرافیکی | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | نرم‌افزار مستندسازی پرستاری | نرم‌افزار برنامه‌ریزی نوبت بیمار | نرم‌افزار ردیابی بیمار | نرم‌افزار مستندسازی ملزومات | نرم‌افزار ارتباطی جریان کار جراحی</t>
+          <t>نرم‌افزار پایگاه داده | نرم‌افزار پرونده الکترونیک سلامت EMR | نرم‌افزار ایمیل | Google Drive | نرم‌افزار گرافیکی | نرم‌افزار MEDITECH | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Windows | Microsoft Word | نرم‌افزار مستندسازی پرستاری | نرم‌افزار برنامه‌ریزی نوبت بیمار | نرم‌افزار ردیابی بیمار | نرم‌افزار مستندسازی ملزومات | نرم‌افزار ارتباطی جریان کار جراحی</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>مانیتورینگ | گوش دادن فعال | سخن گفتن | تفکر انتقادی | استراتژی‌های یادگیری | یادگیری فعال | درک مطلب خواندن</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و پرسنلی | پزشکی و دندانپزشکی | زبان انگلیسی | آموزش و تربیت</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مشکلات | بینایی نزدیک | تشخیص گفتار | ثبات دست و بازو | زبردستی دست | توجه انتخابی | سرعت ادراکی | بیان شفاهی | سازماندهی اطلاعات | سهولت کار با اعداد | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص رنگ بصری | بینایی دور | قدرت تنه | هماهنگی چند عضو | دقت کنترل | زبردستی انگشتان | تجسم فضایی | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | ثبات دست و بازو | مهارت دستی | توجه انتخابی | سرعت ادراکی | بیان شفاهی | ترتیب‌دهی اطلاعات | توانایی عددی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص رنگ بصری | بینایی دور | قدرت تنه | هماهنگی چند عضو | دقت کنترل | مهارت انگشتان | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>نزدیکی فیزیکی | اهمیت دقیق یا منظم بودن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | داخل ساختمان، محیط کنترل‌شده | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تاثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | صرف زمان برای ایستادن | پیامد اشتباه | قرار گرفتن در معرض آلاینده‌ها | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، مهار ایمنی، لباس‌های محافظ کامل یا محافظ تشعشع</t>
+          <t>نزدیکی فیزیکی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | فراوانی تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | صرف زمان برای ایستادن | پیامد خطا | قرار گرفتن در معرض آلاینده‌ها | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | پیامدهای کاری و نتایج سایر کارکنان | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | آزادی در تصمیم‌گیری | صرف زمان برای انجام حرکات تکراری | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | تکنولوژیست‌ها و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیص پزشکی | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های آندوسکوپی | هیستوتکنولوژیست‌ها | دستیاران پزشک | آماده‌سازان تجهیزات پزشکی | تکنسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | پرستاران بیهوشی | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | جراحان ارتوپد، به جز اطفال | جراحان اطفال | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | درمانگران تنفسی | دستیاران جراحی</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | تکنولوژیست‌ها و تکنیسین‌های قلبی-عروقی | سونوگرافیست‌های پزشکی تشخیصی | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های آندوسکوپی | هیستوتکنولوژیست‌ها | دستیاران پزشکی | آماده‌سازان تجهیزات پزشکی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های نورودیاگنوستیک | پرستاران بیهوشی | تکنسین‌های پزشکی چشم‌پزشکی | تکنولوژیست‌های پزشکی چشم‌پزشکی | جراحان ارتوپد، به‌جز کودکان | جراحان کودکان | پرتودرمانگران | تکنولوژیست‌ها و تکنسین‌های رادیولوژی | درمانگران تنفسی | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0049_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0049_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | نظارت | نگارش | علوم تجربی | ریاضیات | یادگیری فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | نگارش | علوم | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زیست‌شناسی | زبان انگلیسی | فیزیک | پزشکی و دندان‌پزشکی | شیمی | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | امور اداری و دفتری | آموزش و تدریس | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زیست‌شناسی | زبان انگلیسی | فیزیک | پزشکی و دندان‌پزشکی | شیمی | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی | اداری | آموزش و پرورش | روان‌شناسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | حساسیت به مسئله | درک کتبی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | استدلال قیاسی | بیان کتبی | انعطاف‌پذیری در طبقه‌بندی | سهولت کار با اعداد | استدلال ریاضی | دقت کنترل | ثبات دست و بازو | سرعت ادراک | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | درک کتبی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | استدلال قیاسی | بیان کتبی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | استدلال ریاضی | دقت کنترل | ثبات دست و بازو | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>دستیاران بیهوشی | متخصصان قلب و عروق | تکنسین‌ها و کارشناسان قلب و عروق | تکنسین‌های سیتوژنتیک | سونوگرافیست‌های تشخیصی پزشکی | پزشکان طب اورژانس | تکنسین‌های بافت‌شناسی | کارشناسان بافت‌شناسی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | دزیمتریست‌های پزشکی | آماده‌سازان تجهیزات پزشکی | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | تکنسین‌های تشخیص بالینی اعصاب | تکنسین‌های پایش هسته‌ای | کارشناسان تجهیزات تشخیصی چشم‌پزشکی | پرتودرمانگران (رادیوتراپیست‌ها) | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | رادیولوژیست‌ها (متخصصان رادیولوژی) | تکنسین‌های اتاق عمل (تکنسین‌های جراحی)</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | کارشناسان سیتوژنتیک | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | پزشکان طب اورژانس | کاردان‌های پاتولوژی و بافت‌شناسی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | دزیمتریست‌های پزشکی | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | تکنسین‌های الکترونورودیاگنوستیک | تکنسین‌های پایش و حفاظت پرتوی | کارشناسان فناوری پزشکی چشم | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | نظارت | تفکر انتقادی | نگارش</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نظارت | تفکر انتقادی | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | رایانه و الکترونیک | امور اداری و دفتری | آموزش و تدریس | ایمنی و امنیت عمومی | روان‌شناسی | فیزیک | زیست‌شناسی</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | زبان انگلیسی | رایانه و الکترونیک | اداری | آموزش و پرورش | ایمنی و امنیت عمومی | روان‌شناسی | فیزیک | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید نزدیک | بیان شفاهی | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | استدلال استقرایی | سرعت ادراک | انعطاف‌پذیری بستار | انعطاف‌پذیری در طبقه‌بندی | دقت کنترل | ثبات دست و بازو | توجه انتخابی | تجسم فضایی | بیان کتبی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | بیان شفاهی | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | استدلال استقرایی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | دقت کنترل | ثبات دست و بازو | توجه انتخابی | تجسم | بیان کتبی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>دستیاران بیهوشی | متخصصان قلب و عروق | تکنسین‌ها و کارشناسان قلب و عروق | سونوگرافیست‌های تشخیصی پزشکی | تکنسین‌های آندوسکوپی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | دستیاران پزشکی | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | تکنسین‌های تشخیص بالینی اعصاب | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های تجهیزات تشخیصی چشم‌پزشکی | کارشناسان تجهیزات تشخیصی چشم‌پزشکی | جراحان ارتوپد، به‌جز اطفال | جراحان کودکان | پرتودرمانگران (رادیوتراپیست‌ها) | رادیولوژیست‌ها (متخصصان رادیولوژی) | درمانگران تنفسی | دستیاران جراحی | تکنسین‌های اتاق عمل (تکنسین‌های جراحی)</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | تکنسین‌های اندوسکوپی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کمک‌پزشکان و دستیاران مطب | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | پرتودرمانگران / کارشناسان رادیوتراپی | متخصصان رادیولوژی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نظارت | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | فیزیک | رایانه و الکترونیک | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | آموزش و تدریس | زیست‌شناسی | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | فیزیک | رایانه و الکترونیک | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی | آموزش و پرورش | زیست‌شناسی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | دید نزدیک | درک کتبی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | دقت کنترل | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری بستار | انعطاف‌پذیری در طبقه‌بندی | چابکی انگشتان | چابکی دستی | ثبات دست و بازو | توجه انتخابی | سرعت ادراک | دید دور</t>
+          <t>درک شفاهی | بیان شفاهی | بینایی نزدیک | درک کتبی | حساسیت به مسئله | بیان کتبی | استدلال قیاسی | دقت کنترل | تشخیص گفتار | وضوح گفتار | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | مهارت انگشتان | مهارت دستی | ثبات دست و بازو | توجه انتخابی | سرعت ادراکی | بینایی دور</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>دستیاران بیهوشی | متخصصان قلب و عروق | تکنسین‌ها و کارشناسان قلب و عروق | تکنسین‌های سیتوژنتیک | سونوگرافیست‌های تشخیصی پزشکی | تکنسین‌های آندوسکوپی | دزیمتریست‌های پزشکی | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | تکنسین‌های تشخیص بالینی اعصاب | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های تجهیزات تشخیصی چشم‌پزشکی | کارشناسان تجهیزات تشخیصی چشم‌پزشکی | جراحان ارتوپد، به‌جز اطفال | جراحان کودکان | پرتودرمانگران (رادیوتراپیست‌ها) | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | رادیولوژیست‌ها (متخصصان رادیولوژی) | درمانگران تنفسی | تکنسین‌های اتاق عمل (تکنسین‌های جراحی)</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | کارشناسان سیتوژنتیک | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | تکنسین‌های اندوسکوپی | دزیمتریست‌های پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | تکنسین‌های اتاق عمل</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,22 +674,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>محیط توسعه Eclipse IDE | سیستم‌های Epic Systems | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری بیماری‌ها و اقدامات پزشکی</t>
+          <t>محیط توسعه Eclipse IDE | سیستم‌های Epic Systems | نرم‌افزار MEDITECH | نرم‌افزار کدگذاری شرایط پزشکی</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | نگارش | ریاضیات | نظارت | علوم تجربی | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | ریاضیات | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ریاضیات | فیزیک | رایانه و الکترونیک | زیست‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | طراحی | آموزش و تدریس | خدمات مشتریان و خدمات فردی</t>
+          <t>ریاضیات | فیزیک | رایانه و الکترونیک | زیست‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | طراحی | آموزش و پرورش | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | استدلال ریاضی | سهولت کار با اعداد | انعطاف‌پذیری بستار | روانی کلام و ایده | دید دور | توجه انتخابی | تجسم فضایی | سرعت ادراک | ابتکار و اصالت</t>
+          <t>استدلال قیاسی | استدلال استقرایی | درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | توانایی عددی | انعطاف‌پذیری بستار | روانی ایده‌ها | بینایی دور | توجه انتخابی | تجسم | سرعت ادراکی | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>دستیاران بیهوشی | مهندسان زیستی و مهندسان پزشکی | متخصصان قلب و عروق | تکنسین‌ها و کارشناسان قلب و عروق | سونوگرافیست‌های تشخیصی پزشکی | تکنسین‌های فوریت‌های پزشکی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | تکنسین‌های تشخیص بالینی اعصاب | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های پایش هسته‌ای | پرستاران بیهوشی | جراحان ارتوپد، به‌جز اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان کودکان | پرتودرمانگران (رادیوتراپیست‌ها) | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | رادیولوژیست‌ها (متخصصان رادیولوژی) | درمانگران تنفسی</t>
+          <t>دستیاران متخصص بیهوشی | مهندسان پزشکی و بیوانجینیرینگ | متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | تکنسین‌های فوریت‌های پزشکی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | تکنسین‌های الکترونورودیاگنوستیک | کارشناسان و تکنسین‌های پزشکی هسته‌ای | تکنسین‌های پایش و حفاظت پرتوی | پرستاران بیهوشی | جراحان ارتوپدی، غیر از اطفال | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | جراحان اطفال | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم تجربی | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی | روان‌شناسی | زیست‌شناسی | حمل‌ونقل و ترابری | درمان و مشاوره‌گری</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | روان‌شناسی | زیست‌شناسی | حمل و نقل | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | ثبات دست و بازو | چابکی دستی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | تجسم فضایی | تسهیم زمان و توجه | زمان واکنش | قدرت ایستا | قدرت تنه | استقامت جسمانی | توجه شنیداری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | زمان عکس‌العمل | قدرت ایستا | قدرت تنه | استقامت | توجه شنیداری</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت حاد | رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | دستیاران بیهوشی | متخصصان بیهوشی | تکنسین‌ها و کارشناسان قلب و عروق | پرستاران مراقبت‌های ویژه (ICU) | پزشکان طب اورژانس | مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشکی | پرستاران بیهوشی | پرستاران دوره‌دیده (پرستاران متخصص) | کمک‌بهیاران | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | دستیاران فیزیوتراپی | دستیاران پزشک | تکنسین‌های روان‌پزشکی | پرستاران رسمی | درمانگران تنفسی | دستیاران جراحی</t>
+          <t>پرستاران مراقبت‌های حاد | رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | کارشناسان و تکنسین‌های قلب و عروق | پرستاران مراقبت‌های ویژه | پزشکان طب اورژانس | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | پرستاران بیهوشی | پرستاران بالینی پیشرفته | کمک‌پرستاران | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | کمک‌یاران فیزیوتراپی | دستیاران پزشک | تکنسین‌های روان‌پزشکی و بهداشت روان | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | علوم تجربی | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | علوم | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی | روان‌شناسی | زیست‌شناسی | شیمی | حمل‌ونقل و ترابری | درمان و مشاوره‌گری</t>
+          <t>پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | روان‌شناسی | زیست‌شناسی | شیمی | حمل و نقل | درمان و مشاوره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | چابکی انگشتان | ثبات دست و بازو | چابکی دستی | توجه انتخابی | انعطاف‌پذیری در طبقه‌بندی | تجسم فضایی | تسهیم زمان و توجه | زمان واکنش | قدرت ایستا | قدرت تنه | استقامت جسمانی | توجه شنیداری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | تجسم | تقسیم توجه | زمان عکس‌العمل | قدرت ایستا | قدرت تنه | استقامت | توجه شنیداری</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت حاد | رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | دستیاران بیهوشی | متخصصان بیهوشی | تکنسین‌ها و کارشناسان قلب و عروق | پرستاران بالینی متخصص | پرستاران مراقبت‌های ویژه (ICU) | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشکی | پرستاران بیهوشی | ماماها | پرستاران دوره‌دیده (پرستاران متخصص) | کمک‌بهیاران | دستیاران پزشک | پرستاران رسمی | درمانگران تنفسی | دستیاران جراحی</t>
+          <t>پرستاران مراقبت‌های حاد | رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | دستیاران متخصص بیهوشی | متخصصان بیهوشی | کارشناسان و تکنسین‌های قلب و عروق | پرستاران متخصص بالینی | پرستاران مراقبت‌های ویژه | تکنسین‌های فوریت‌های پزشکی | پزشکان طب اورژانس | پزشکان عمومی و خانواده | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | پرستاران بیهوشی | ماماهای پرستار | پرستاران بالینی پیشرفته | کمک‌پرستاران | دستیاران پزشک | پرستاران | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نگارش | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری | نظارت | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | آموزش و تدریس | ریاضیات | ایمنی و امنیت عمومی | مدیریت و امور اداری | تولید مواد غذایی | امور اداری و دفتری | رایانه و الکترونیک | تولید و فراوری | پرسنل و منابع انسانی | حقوق و مقررات دولتی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | ریاضیات | ایمنی و امنیت عمومی | مدیریت و اداره | تولید مواد غذایی | اداری | رایانه و الکترونیک | تولید و فرآوری | پرسنل و منابع انسانی | قانون و دولت</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | دید نزدیک | وضوح گفتار | درک کتبی | حساسیت به مسئله | استدلال استقرایی | انعطاف‌پذیری در طبقه‌بندی | مرتب‌سازی اطلاعات | روانی کلام و ایده | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری بستار | ابتکار و اصالت</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | بینایی نزدیک | وضوح گفتار | درک کتبی | حساسیت به مسئله | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | روانی ایده‌ها | بیان کتبی | تشخیص گفتار | انعطاف‌پذیری بستار | اصالت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>متخصصان آلرژی و ایمونولوژی | پرستاران بالینی متخصص | رابطان و مروجان سلامت جامعه | آشپزهای سازمانی، بیمارستانی و سلف‌سرویس | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | فیزیولوژیست‌های ورزشی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | هماهنگ‌کنندگان تناسب اندام و سلامت | دانشمندان و فناوران صنایع غذایی | مدیران خدمات پذیرایی و غذا | کارشناسان آموزش و ارتقای سلامت | مراقبان سلامت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشکی | مدیران خدمات بهداشتی و درمانی | کمک‌بهیاران | پزشکان طب پیشگیری | تکنسین‌های روان‌پزشکی | پرستاران رسمی | مشاوران توانبخشی</t>
+          <t>متخصصان آلرژی و ایمنی‌شناسی | پرستاران متخصص بالینی | رابطان سلامت و بهورزان | آشپزان مراکز پخت گروهی و سلف‌سرویس‌ها | کارشناسان و متخصصان تغذیه و رژیم‌درمانی | فیزیولوژیست‌های ورزشی | مدرسان علوم خانواده و مدیریت مصرف در آموزش عالی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | متخصصان و کارشناسان علوم و صنایع غذایی | مدیران خدمات پذیرایی و غذا و نوشیدنی | کارشناسان آموزش بهداشت و ارتقای سلامت | مراقبان سلامت و بهیاران مراقبت در منزل | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | مدیران خدمات درمانی و بهداشتی | کمک‌پرستاران | متخصصان پزشکی اجتماعی و طب پیشگیری | تکنسین‌های روان‌پزشکی و بهداشت روان | پرستاران | مشاوران توانبخشی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | نگارش | ریاضیات</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | نگارش | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | حقوق و مقررات دولتی | امور اداری و دفتری | تولید و فراوری</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | قانون و دولت | اداری | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | دید نزدیک | تشخیص گفتار | مرتب‌سازی اطلاعات | حساسیت به مسئله | انعطاف‌پذیری در طبقه‌بندی | وضوح گفتار | بیان کتبی | چابکی انگشتان | سرعت ادراک | سهولت کار با اعداد | استدلال قیاسی | ثبات دست و بازو | تسهیم زمان و توجه | توجه انتخابی | استدلال استقرایی | چابکی دستی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بینایی نزدیک | تشخیص گفتار | ترتیب‌دهی اطلاعات | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | بیان کتبی | مهارت انگشتان | سرعت ادراکی | توانایی عددی | استدلال قیاسی | ثبات دست و بازو | تقسیم توجه | توجه انتخابی | استدلال استقرایی | مهارت دستی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>دستیاران بیهوشی | تکنسین‌ها و کارشناسان قلب و عروق | دستیاران دندان‌پزشکی | بهیاران و کمک‌پرستاران دارای مجوز | دستیاران پزشکی | آماده‌سازان تجهیزات پزشکی | متخصصان اسناد و مدارک پزشکی | متصدیان پذیرش و منشی‌های بخش پزشکی | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان آزمایشگاه پزشکی و بالینی | مدیران خدمات بهداشتی و درمانی | کمک‌بهیاران | تکنسین‌های تجهیزات تشخیصی چشم‌پزشکی | عینک‌سازان (ساخت و فروش عینک) | داروسازان | دستیاران و کمک‌کارکنان داروخانه | تکنسین‌های خون‌گیری (خون‌گیرها) | دستیاران جراحی | تکنسین‌های اتاق عمل (تکنسین‌های جراحی) | کارشناسان و تکنسین‌های دامپزشکی</t>
+          <t>دستیاران متخصص بیهوشی | کارشناسان و تکنسین‌های قلب و عروق | دستیاران دندان‌پزشک | بهیاران و کمک‌پرستاران دارای مجوز | کمک‌پزشکان و دستیاران مطب | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کارشناسان و تکنسین‌های مدارک پزشکی و فناوری اطلاعات سلامت | منشی‌ها و متصدیان پذیرش مراکز پزشکی و درمانی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | مدیران خدمات درمانی و بهداشتی | کمک‌پرستاران | تکنسین‌های مراقبت‌های چشمی | عینک‌سازان (ساخت و فروش عینک) | داروسازان | کمک‌متصدیان داروخانه | کارشناسان و تکنسین‌های خون‌گیری | دستیاران جراحی | تکنسین‌های اتاق عمل | تکنسین‌ها و کارشناسان فناوری دامپزشکی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>روان‌شناسی | درمان و مشاوره‌گری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | آموزش و تدریس | ایمنی و امنیت عمومی | حقوق و مقررات دولتی | رایانه و الکترونیک | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>روان‌شناسی | درمان و مشاوره | زبان انگلیسی | خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | آموزش و پرورش | ایمنی و امنیت عمومی | قانون و دولت | رایانه و الکترونیک | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | دید نزدیک | مرتب‌سازی اطلاعات | توجه انتخابی | دید دور | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | تشخیص گفتار | وضوح گفتار | بیان کتبی | بینایی نزدیک | ترتیب‌دهی اطلاعات | توجه انتخابی | بینایی دور | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>پرستاران مراقبت حاد | پرستاران بالینی پیشرفته روان‌پزشکی | پرستاران بالینی متخصص | روان‌شناسان بالینی و مشاور | مراقبان سلامت در منزل | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و سوءمصرف مواد | پرستاران دوره‌دیده (پرستاران متخصص) | کاردرمانگران | دستیاران خدماتی کاردرمانی | کاردان‌های کاردرمانی | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | پزشکان طب فیزیکی و توانبخشی | دستیاران فیزیوتراپی | کاردان‌های فیزیوتراپی | فیزیوتراپ‌ها | بهیاران و کمک‌مراقبان بخش روان‌پزشکی | روان‌پزشکان | درمانگران تفریحی | پرستاران رسمی</t>
+          <t>پرستاران مراقبت‌های حاد | پرستاران تخصصی روانپزشکی | پرستاران متخصص بالینی | روان‌شناسان بالینی و مشاوران سلامت روان | مراقبان سلامت و بهیاران مراقبت در منزل | مشاوران سلامت روان | مددکاران اجتماعی حوزه سلامت روان و اعتیاد | پرستاران بالینی پیشرفته | کاردرمانگران | کمک‌یاران کاردرمانی | کاردان‌های کاردرمانی | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | متخصصان طب فیزیکی و توانبخشی | کمک‌یاران فیزیوتراپی | کاردان‌های فیزیوتراپی | فیزیوتراپیست‌ها | کمک‌یاران بخش روان‌پزشکی | روان‌پزشکان | کارشناسان تفریح‌درمانی | پرستاران</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | سخن گفتن | تفکر انتقادی | استراتژی‌های یادگیری | یادگیری فعال | درک مطلب</t>
+          <t>نظارت | گوش دادن فعال | سخن گفتن | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید نزدیک | تشخیص گفتار | ثبات دست و بازو | چابکی دستی | توجه انتخابی | سرعت ادراک | بیان شفاهی | مرتب‌سازی اطلاعات | سهولت کار با اعداد | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص تمایز رنگ‌ها | دید دور | قدرت تنه | هماهنگی اندام‌ها | دقت کنترل | چابکی انگشتان | تجسم فضایی | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی نزدیک | تشخیص گفتار | ثبات دست و بازو | مهارت دستی | توجه انتخابی | سرعت ادراکی | بیان شفاهی | ترتیب‌دهی اطلاعات | توانایی عددی | انعطاف‌پذیری بستار | وضوح گفتار | تشخیص رنگ بصری | بینایی دور | قدرت تنه | هماهنگی چند عضو | دقت کنترل | مهارت انگشتان | تجسم | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | استدلال قیاسی | بیان کتبی | درک کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>دستیاران بیهوشی | متخصصان بیهوشی | تکنسین‌ها و کارشناسان قلب و عروق | سونوگرافیست‌های تشخیصی پزشکی | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های آندوسکوپی | کارشناسان بافت‌شناسی | دستیاران پزشکی | آماده‌سازان تجهیزات پزشکی | تکنسین‌های آزمایشگاه پزشکی و بالینی | تکنسین‌های تشخیص بالینی اعصاب | پرستاران بیهوشی | تکنسین‌های تجهیزات تشخیصی چشم‌پزشکی | کارشناسان تجهیزات تشخیصی چشم‌پزشکی | جراحان ارتوپد، به‌جز اطفال | جراحان کودکان | پرتودرمانگران (رادیوتراپیست‌ها) | تکنسین‌ها و کارشناسان رادیولوژی و پرتونگاری | درمانگران تنفسی | دستیاران جراحی</t>
+          <t>دستیاران متخصص بیهوشی | متخصصان بیهوشی | کارشناسان و تکنسین‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | تکنسین‌های فوریت‌های پزشکی | تکنسین‌های اندوسکوپی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | کمک‌پزشکان و دستیاران مطب | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | تکنسین‌های الکترونورودیاگنوستیک | پرستاران بیهوشی | تکنسین‌های مراقبت‌های چشمی | کارشناسان فناوری پزشکی چشم | جراحان ارتوپدی، غیر از اطفال | جراحان اطفال | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران | دستیاران جراحی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
